--- a/Master/2025_and_2026/JSS3.xlsx
+++ b/Master/2025_and_2026/JSS3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\Master\2025_and_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDEFCCC-C0E9-4D03-9E35-2295D0E9AFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF57C794-4359-4F73-8AF9-82F7B3D85A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E1CAD310-787C-4423-8550-9AEB673BF233}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="106">
   <si>
     <t>Civic Education</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Three</t>
   </si>
   <si>
-    <t>default.jfif</t>
-  </si>
-  <si>
     <t>TEST</t>
   </si>
   <si>
@@ -210,27 +207,9 @@
     <t>saddy@gmail.com</t>
   </si>
   <si>
-    <t>14, kolawole str</t>
-  </si>
-  <si>
-    <t>+2348090650910</t>
-  </si>
-  <si>
-    <t>saddy344@gmail.com</t>
-  </si>
-  <si>
-    <t>14, Giwa Onilu str</t>
-  </si>
-  <si>
     <t>Lagos</t>
   </si>
   <si>
-    <t>saddyand myles@gmail.com</t>
-  </si>
-  <si>
-    <t>saddy124@gmail.com</t>
-  </si>
-  <si>
     <t>Agricultural Science</t>
   </si>
   <si>
@@ -243,61 +222,127 @@
     <t>society</t>
   </si>
   <si>
-    <t>Alimosho</t>
-  </si>
-  <si>
     <t>Press Club</t>
   </si>
   <si>
     <t>Boys Scout</t>
   </si>
   <si>
-    <t>Epe</t>
-  </si>
-  <si>
     <t>JETS Club</t>
   </si>
   <si>
     <t>Girls Guide</t>
   </si>
   <si>
-    <t>Shomolu</t>
-  </si>
-  <si>
     <t>Sex Edu Club</t>
   </si>
   <si>
     <t>Red Cross</t>
   </si>
   <si>
-    <t>Ibeju-Lekki</t>
-  </si>
-  <si>
     <t>Farmers Club</t>
   </si>
   <si>
     <t>Boys Brigade</t>
   </si>
   <si>
-    <t>Etiosa</t>
-  </si>
-  <si>
     <t>English Club</t>
   </si>
   <si>
-    <t>Badagry</t>
-  </si>
-  <si>
     <t>Maths Club</t>
   </si>
   <si>
-    <t>Lagos-Island</t>
-  </si>
-  <si>
-    <t>Chess Club</t>
-  </si>
-  <si>
     <t>Mushin</t>
+  </si>
+  <si>
+    <t>j36.jpg</t>
+  </si>
+  <si>
+    <t>27/5/2012</t>
+  </si>
+  <si>
+    <t>Osun</t>
+  </si>
+  <si>
+    <t>Irepodun</t>
+  </si>
+  <si>
+    <t>azeezahadelani@gmail.com</t>
+  </si>
+  <si>
+    <t>Ikotun, Lagos</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Ogun</t>
+  </si>
+  <si>
+    <t>Remo North</t>
+  </si>
+  <si>
+    <t>islamiyahawobola@gmail.com</t>
+  </si>
+  <si>
+    <t>16/11/2011</t>
+  </si>
+  <si>
+    <t>julianahawolola9@gmail.com</t>
+  </si>
+  <si>
+    <t>Oyo</t>
+  </si>
+  <si>
+    <t>Kajola</t>
+  </si>
+  <si>
+    <t>20/03/2012</t>
+  </si>
+  <si>
+    <t>monsuraholasupo@gmail.com</t>
+  </si>
+  <si>
+    <t>umarsemiu0@gmail.com</t>
+  </si>
+  <si>
+    <t>Ogun Waterside</t>
+  </si>
+  <si>
+    <t>muthmainahtijani9@gmail.com</t>
+  </si>
+  <si>
+    <t>Oluyole</t>
+  </si>
+  <si>
+    <t>samodyusuf79@gmail.com</t>
+  </si>
+  <si>
+    <t>Kwara</t>
+  </si>
+  <si>
+    <t>Ilorin-west</t>
   </si>
 </sst>
 </file>
@@ -679,10 +724,10 @@
     <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.453125" customWidth="1"/>
     <col min="8" max="8" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.08984375" customWidth="1"/>
     <col min="10" max="10" width="22.36328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="21.08984375" bestFit="1" customWidth="1"/>
@@ -693,74 +738,75 @@
     <col min="20" max="20" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>42</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" t="s">
-        <v>46</v>
-      </c>
       <c r="G1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>55</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>56</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>57</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" t="s">
         <v>58</v>
       </c>
-      <c r="L1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M1" t="s">
-        <v>59</v>
-      </c>
       <c r="N1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="O1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="P1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="Q1" t="s">
         <v>0</v>
       </c>
       <c r="R1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" t="s">
         <v>49</v>
-      </c>
-      <c r="S1" t="s">
-        <v>1</v>
-      </c>
-      <c r="T1" t="s">
-        <v>50</v>
       </c>
       <c r="U1" t="s">
         <v>2</v>
       </c>
       <c r="V1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W1" t="s">
         <v>3</v>
@@ -775,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="AA1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AB1" t="s">
         <v>7</v>
@@ -784,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="AD1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
@@ -795,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
@@ -807,31 +853,31 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="K2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" s="3">
-        <v>37904</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="O2" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -843,6 +889,9 @@
         <v>1</v>
       </c>
       <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
@@ -881,10 +930,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -893,31 +942,31 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="J3" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3" s="3">
-        <v>37691</v>
+        <v>91</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -929,6 +978,9 @@
         <v>1</v>
       </c>
       <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
@@ -967,10 +1019,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -979,31 +1031,31 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s">
-        <v>78</v>
-      </c>
-      <c r="M4" s="3">
-        <v>37967</v>
+        <v>96</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -1015,6 +1067,9 @@
         <v>1</v>
       </c>
       <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
         <v>1</v>
       </c>
       <c r="U4">
@@ -1053,10 +1108,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1065,31 +1120,31 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="J5" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="L5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M5" s="3">
-        <v>37665</v>
+        <v>39970</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -1101,6 +1156,9 @@
         <v>1</v>
       </c>
       <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
       <c r="U5">
@@ -1139,10 +1197,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -1151,31 +1209,31 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="J6" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="M6" s="3">
-        <v>37755</v>
+        <v>41101</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -1187,6 +1245,9 @@
         <v>1</v>
       </c>
       <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
         <v>1</v>
       </c>
       <c r="U6">
@@ -1225,43 +1286,43 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="M7" s="3">
-        <v>37636</v>
+        <v>40978</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -1273,6 +1334,9 @@
         <v>1</v>
       </c>
       <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
         <v>1</v>
       </c>
       <c r="U7">
@@ -1311,10 +1375,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -1323,31 +1387,31 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="J8" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="L8" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="M8" s="3">
-        <v>37880</v>
+        <v>40920</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -1359,6 +1423,9 @@
         <v>1</v>
       </c>
       <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
         <v>1</v>
       </c>
       <c r="U8">
@@ -1397,10 +1464,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
@@ -1409,31 +1476,31 @@
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" t="s">
         <v>60</v>
       </c>
-      <c r="J9" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" t="s">
-        <v>65</v>
-      </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="M9" s="3">
         <v>37850</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1445,6 +1512,9 @@
         <v>1</v>
       </c>
       <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
         <v>1</v>
       </c>
       <c r="U9">
@@ -1482,6 +1552,10 @@
     <hyperlink ref="I3:I9" r:id="rId2" display="saddy@gmail.com" xr:uid="{CAC1E7E9-7609-4846-B89F-F775428CEC3F}"/>
     <hyperlink ref="I5" r:id="rId3" xr:uid="{B47BD398-3386-405A-BC5B-F76E6AD4C550}"/>
     <hyperlink ref="I4" r:id="rId4" xr:uid="{A039FE2B-E2AE-4A3B-9501-10DAF7E8E73A}"/>
+    <hyperlink ref="I3" r:id="rId5" xr:uid="{30E624FE-4AEB-45DE-B49F-410B37135D8C}"/>
+    <hyperlink ref="I6" r:id="rId6" xr:uid="{9627DA50-6C3B-41F5-B476-AE62CE8214AB}"/>
+    <hyperlink ref="I7" r:id="rId7" xr:uid="{35A3D0B7-E9CF-42EA-8821-BDB489FC5851}"/>
+    <hyperlink ref="I8" r:id="rId8" xr:uid="{AECDE50A-891A-4DAA-AEA8-CA7FA46936B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Master/2025_and_2026/JSS3.xlsx
+++ b/Master/2025_and_2026/JSS3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\Master\2025_and_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF57C794-4359-4F73-8AF9-82F7B3D85A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9102084-69CF-4FF2-9B8C-1AC344CF6ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E1CAD310-787C-4423-8550-9AEB673BF233}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
   <si>
     <t>Civic Education</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Ayoka</t>
   </si>
   <si>
-    <t>Abdul-Somod</t>
-  </si>
-  <si>
     <t>Three</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>Islamiyah</t>
   </si>
   <si>
-    <t>Julianah</t>
-  </si>
-  <si>
     <t>Monsurah</t>
   </si>
   <si>
@@ -343,6 +337,21 @@
   </si>
   <si>
     <t>Ilorin-west</t>
+  </si>
+  <si>
+    <t>Basic Science</t>
+  </si>
+  <si>
+    <t>Basic Tech</t>
+  </si>
+  <si>
+    <t>Business Studies</t>
+  </si>
+  <si>
+    <t>Abdulsamod</t>
+  </si>
+  <si>
+    <t>Juliana</t>
   </si>
 </sst>
 </file>
@@ -393,11 +402,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -713,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD0AD9F-73A2-4430-B0A6-85C76F292A51}">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
@@ -739,101 +751,111 @@
     <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R1" t="s">
+        <v>105</v>
+      </c>
+      <c r="S1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W1" t="s">
+        <v>47</v>
+      </c>
+      <c r="X1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="Z1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" t="s">
-        <v>64</v>
-      </c>
-      <c r="P1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>0</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="AE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG1" t="s">
         <v>48</v>
       </c>
-      <c r="S1" t="s">
-        <v>1</v>
-      </c>
-      <c r="T1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W1" t="s">
-        <v>3</v>
-      </c>
-      <c r="X1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>50</v>
-      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>23001</v>
       </c>
@@ -841,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
@@ -853,31 +875,31 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -903,15 +925,15 @@
       <c r="W2">
         <v>1</v>
       </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
         <v>1</v>
       </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
       <c r="AB2">
         <v>1</v>
       </c>
@@ -921,8 +943,17 @@
       <c r="AD2">
         <v>1</v>
       </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>23002</v>
       </c>
@@ -930,10 +961,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -942,31 +973,31 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="N3" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -992,15 +1023,15 @@
       <c r="W3">
         <v>1</v>
       </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
         <v>1</v>
       </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
       <c r="AB3">
         <v>1</v>
       </c>
@@ -1010,8 +1041,17 @@
       <c r="AD3">
         <v>1</v>
       </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>23003</v>
       </c>
@@ -1019,10 +1059,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -1031,31 +1071,31 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s">
         <v>94</v>
       </c>
-      <c r="J4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="M4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="L4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="N4" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -1078,15 +1118,15 @@
       <c r="V4">
         <v>1</v>
       </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
         <v>1</v>
       </c>
-      <c r="Z4">
-        <v>1</v>
-      </c>
       <c r="AA4">
         <v>1</v>
       </c>
@@ -1099,8 +1139,17 @@
       <c r="AD4">
         <v>1</v>
       </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>23004</v>
       </c>
@@ -1108,10 +1157,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1120,31 +1169,31 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M5" s="3">
         <v>39970</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -1170,15 +1219,15 @@
       <c r="W5">
         <v>1</v>
       </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
         <v>1</v>
       </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
       <c r="AB5">
         <v>1</v>
       </c>
@@ -1188,8 +1237,17 @@
       <c r="AD5">
         <v>1</v>
       </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>23005</v>
       </c>
@@ -1197,10 +1255,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -1209,31 +1267,31 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M6" s="3">
         <v>41101</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -1259,15 +1317,15 @@
       <c r="W6">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
         <v>1</v>
       </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
       <c r="AB6">
         <v>1</v>
       </c>
@@ -1277,8 +1335,17 @@
       <c r="AD6">
         <v>1</v>
       </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>23006</v>
       </c>
@@ -1286,43 +1353,43 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M7" s="3">
         <v>40978</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -1348,15 +1415,15 @@
       <c r="W7">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
         <v>1</v>
       </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
       <c r="AB7">
         <v>1</v>
       </c>
@@ -1366,8 +1433,17 @@
       <c r="AD7">
         <v>1</v>
       </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>23007</v>
       </c>
@@ -1375,43 +1451,43 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" t="s">
         <v>103</v>
-      </c>
-      <c r="J8" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" t="s">
-        <v>105</v>
       </c>
       <c r="M8" s="3">
         <v>40920</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -1437,15 +1513,15 @@
       <c r="W8">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
         <v>1</v>
       </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
       <c r="AB8">
         <v>1</v>
       </c>
@@ -1455,8 +1531,17 @@
       <c r="AD8">
         <v>1</v>
       </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>23008</v>
       </c>
@@ -1464,43 +1549,43 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M9" s="3">
         <v>37850</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1526,15 +1611,15 @@
       <c r="W9">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
         <v>1</v>
       </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
       <c r="AB9">
         <v>1</v>
       </c>
@@ -1542,6 +1627,15 @@
         <v>1</v>
       </c>
       <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
         <v>1</v>
       </c>
     </row>
